--- a/assets/constructions/examples/ctd_tavs_arbor.xlsx
+++ b/assets/constructions/examples/ctd_tavs_arbor.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,11 +559,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SCB-C32-SDCK3-350</t>
+          <t>DT10-M6-150</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -573,43 +593,45 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>32</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Carbide</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ISO_5609:32</t>
+          <t>ISO_5609:10</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DER:M6</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -621,7 +643,7 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>3.24</v>
+        <v>0.172</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -631,35 +653,41 @@
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DT16-M10-200</t>
+          <t>AVB50-40-7D</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>305</v>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>200</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>200</v>
+        <v>518</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -672,74 +700,88 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Carbide</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>G1/2“</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>ISO_5609:16</t>
+          <t>ISO_5609:50</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>DER:M10</t>
+          <t>PALB_AVH:40</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="n">
-        <v>0.506</v>
-      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
+          <t>2022/PALBIT Главный каталог</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>3618.69</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>332679.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVB40-40-10D</t>
+          <t>SCB-C19-SDCK1-190</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>40</v>
-      </c>
-      <c r="E4" t="n">
-        <v>40</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>240</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>190</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>408</v>
+        <v>190</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -749,70 +791,78 @@
           <t>Steel</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>G1/2“</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ISO_5609:40</t>
+          <t>ISO_5609:19</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>PALB_AVH:40</t>
+          <t>DER_DCK:1</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0.43</v>
+      </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2022/PALBIT Главный каталог</t>
-        </is>
-      </c>
+          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CU-3C801200-C3</t>
+          <t>D60MTTB1000KM40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cylindrical shank to Coromant CaptoⓇ damped adaptor</t>
+          <t>D...TTB-KM</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>80</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E5" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>686</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>1215</v>
+        <v>976</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>976</v>
+      </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
@@ -820,48 +870,60 @@
         <v>1</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Steel</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>RP 3/8-19</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>HA-80</t>
+          <t>ISO_5609:60</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ISO_26623:32</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>KENNA_KM40TS</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>WID_KM40</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>58</v>
-      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
-      </c>
+          <t>2017/_widia-2017-FullCatalogue.pdf</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AVB50-40-7D</t>
+          <t>AVB32-32-7D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -871,21 +933,21 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>305</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>190</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>518</v>
+        <v>320</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -903,17 +965,17 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>G1/2“</t>
+          <t>G3/8”</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ISO_5609:50</t>
+          <t>ISO_5609:32</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>PALB_AVH:40</t>
+          <t>PALB_AVH:32</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -930,8 +992,22 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2022/PALBIT Главный каталог</t>
-        </is>
+          <t>2022/ palbit основной каталог.pdf</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2633.72</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>242127.62</v>
       </c>
     </row>
   </sheetData>
